--- a/TKM_Iwi_Hapu_Marae_Database.xlsx
+++ b/TKM_Iwi_Hapu_Marae_Database.xlsx
@@ -21,6 +21,8 @@
     <sheet name="Map_Export" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Tupuna" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Tupuna_Location" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Source" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Claim" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -112,6 +114,50 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Links a tupuna to any number of locations of interest. location_type: Marae | Hapū | Iwi | Place. location_ref: the marae/hapū/iwi name exactly as on the map, or a label for a Place. location_detail: for marae, the Location text as shown on the map (disambiguates same-name marae). latitude/longitude: only for Place. relationship: Born | Lived | Died | Buried | Affiliated | Land interest | Other.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Every source of information gets a row and a colour. Claims reference a source_id so provenance is structural. Add new sources (Waitangi Tribunal reports, MLC minutes, iwi websites…) here first.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">One row per statement a source makes. subject_type: Marae | Hapū | Iwi. relationship: has_hapu | belongs_to_iwi | has_waka | alias_of | located_at | other. object_ref: the hapū/iwi/waka/name named. subject_detail = marae Location text to disambiguate same-name marae. confidence: stated | inferred | contested. The TPK layer's own hapū/iwi are NOT repeated here — they are the live baseline; enter claims only from other sources. Example rows are citations from one Māori Maps page.</t>
         </r>
       </text>
     </comment>
@@ -308,7 +354,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="728">
   <si>
     <t xml:space="preserve">TKM Iwi / Hapū / Marae Database</t>
   </si>
@@ -451,6 +497,15 @@
     <t xml:space="preserve">Your ancestors and the places they connect to (marae, hapū, iwi or a custom point). The web map reads these via gen_data.py; you can also add links on the map itself and export CSV in exactly these columns to paste here.</t>
   </si>
   <si>
+    <t xml:space="preserve">SOURCES AND CLAIMS (provenance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source / Claim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information from anywhere other than the live TPK layer is stored as claims attributed to a source, never merged into the baseline. Each source has a colour; the map draws its claims in that colour and flags conflicts between sources. Enter Māori Maps, Te Ara and whānau information here (or on the map and export).</t>
+  </si>
+  <si>
     <t xml:space="preserve">region_id</t>
   </si>
   <si>
@@ -2240,6 +2295,249 @@
   </si>
   <si>
     <t xml:space="preserve">Custom place: give latitude/longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">licence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">retrieved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight_note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Kāhui Māngai (TKM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tkm.govt.nz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown copyright; check site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#b4432b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crown-recognised representative organisations; hapū/marae lists supplied by those organisations. The baseline layer on the map.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Puni Kōkiri marae layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Government GIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://hub.arcgis.com/datasets/TPK::marae-of-aotearoa/about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC BY 4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinates, hapū and iwi per marae; refreshed from TKM (last data edit Nov 2025). Loaded live, shown in kōkōwai red.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Māori Maps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community-curated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All rights reserved — cite, do not copy wholesale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2f6fbf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Potiki National Trust; fieldwork and marae-submitted updates. Records waka per marae. Entered by hand as citations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Ara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encyclopaedia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://teara.govt.nz/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC BY-NC 3.0 NZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8a5bc4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iwi histories and waka traditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whānau / oral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#d9a21b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kōrero, whakapapa books, MLC minute books held by whānau. Highest weight for our own lines; not for publication.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject_detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object_ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">object_detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page_url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korou Kore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57 Foreshore Road, Ahipara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_hapu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngāti Moroki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/marae/korou-kore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listed as Koroukore on TPK layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has_waka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tinana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/waka/tinana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngāti Pakahi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Māori Maps writes 'Ngāti Pakahi (Te Rarawa)'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">belongs_to_iwi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/mi/hapū/ngāti-pakahi-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPK layer places Ngāti Pākahi marae under Ngāpuhi and Ngāti Kahu — conflict to investigate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tauteihiihi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Ihutai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waihou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Māori Maps: Waihou (Waihou-nui-a-rua)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Related waka also listed: Mamari, Ngātokimatawhaorua</t>
   </si>
 </sst>
 </file>
@@ -2522,160 +2820,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Contact" displayName="Contact" ref="A1:G4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:G4"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="contact_id"/>
-    <tableColumn id="2" name="org_id"/>
-    <tableColumn id="3" name="role"/>
-    <tableColumn id="4" name="full_name"/>
-    <tableColumn id="5" name="phone"/>
-    <tableColumn id="6" name="email"/>
-    <tableColumn id="7" name="notes"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Claim" displayName="Claim" ref="A1:L11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L11"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="claim_id"/>
+    <tableColumn id="2" name="source_id"/>
+    <tableColumn id="3" name="subject_type"/>
+    <tableColumn id="4" name="subject_ref"/>
+    <tableColumn id="5" name="subject_detail"/>
+    <tableColumn id="6" name="relationship"/>
+    <tableColumn id="7" name="object_ref"/>
+    <tableColumn id="8" name="object_detail"/>
+    <tableColumn id="9" name="page_url"/>
+    <tableColumn id="10" name="retrieved"/>
+    <tableColumn id="11" name="confidence"/>
+    <tableColumn id="12" name="note"/>
   </tableColumns>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Tupuna" displayName="Tupuna" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J2"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="tupuna_id"/>
-    <tableColumn id="2" name="name"/>
-    <tableColumn id="3" name="other_names"/>
-    <tableColumn id="4" name="born"/>
-    <tableColumn id="5" name="died"/>
-    <tableColumn id="6" name="birthplace"/>
-    <tableColumn id="7" name="mother"/>
-    <tableColumn id="8" name="father"/>
-    <tableColumn id="9" name="notes"/>
-    <tableColumn id="10" name="source"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Tupuna_Location" displayName="Tupuna_Location" ref="A1:J4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J4"/>
-  <tableColumns count="10">
-    <tableColumn id="1" name="link_id"/>
-    <tableColumn id="2" name="tupuna_id"/>
-    <tableColumn id="3" name="location_type"/>
-    <tableColumn id="4" name="location_ref"/>
-    <tableColumn id="5" name="location_detail"/>
-    <tableColumn id="6" name="latitude"/>
-    <tableColumn id="7" name="longitude"/>
-    <tableColumn id="8" name="relationship"/>
-    <tableColumn id="9" name="notes"/>
-    <tableColumn id="10" name="source"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Hapu" displayName="Hapu" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D11"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="hapu_id"/>
-    <tableColumn id="2" name="hapu_name"/>
-    <tableColumn id="3" name="iwi_id"/>
-    <tableColumn id="4" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Iwi" displayName="Iwi" ref="A1:M118" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M118"/>
-  <tableColumns count="13">
-    <tableColumn id="1" name="iwi_id"/>
-    <tableColumn id="2" name="iwi_name"/>
-    <tableColumn id="3" name="primary_region_id"/>
-    <tableColumn id="4" name="tkm_url"/>
-    <tableColumn id="5" name="mfa_status"/>
-    <tableColumn id="6" name="population"/>
-    <tableColumn id="7" name="population_source"/>
-    <tableColumn id="8" name="rohe_description"/>
-    <tableColumn id="9" name="rohe_map_image_url"/>
-    <tableColumn id="10" name="rohe_document_url"/>
-    <tableColumn id="11" name="rohe_copyright_holder"/>
-    <tableColumn id="12" name="tkm_last_updated"/>
-    <tableColumn id="13" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Iwi_LocalAuthority" displayName="Iwi_LocalAuthority" ref="A1:C5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
-  <tableColumns count="3">
-    <tableColumn id="1" name="iwi_id"/>
-    <tableColumn id="2" name="authority_type"/>
-    <tableColumn id="3" name="authority_name"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Iwi_Region" displayName="Iwi_Region" ref="A1:B128" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:B128"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="iwi_id"/>
-    <tableColumn id="2" name="region_id"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Marae" displayName="Marae" ref="A1:P15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:P15"/>
-  <tableColumns count="16">
-    <tableColumn id="1" name="marae_id"/>
-    <tableColumn id="2" name="marae_name"/>
-    <tableColumn id="3" name="wharenui"/>
-    <tableColumn id="4" name="marae_type"/>
-    <tableColumn id="5" name="address_line"/>
-    <tableColumn id="6" name="locality"/>
-    <tableColumn id="7" name="postcode"/>
-    <tableColumn id="8" name="region_council_area"/>
-    <tableColumn id="9" name="latitude"/>
-    <tableColumn id="10" name="longitude"/>
-    <tableColumn id="11" name="nztm_easting"/>
-    <tableColumn id="12" name="nztm_northing"/>
-    <tableColumn id="13" name="geocode_source"/>
-    <tableColumn id="14" name="geocode_accuracy"/>
-    <tableColumn id="15" name="tkm_url"/>
-    <tableColumn id="16" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Marae_Hapu" displayName="Marae_Hapu" ref="A1:D18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D18"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="marae_id"/>
-    <tableColumn id="2" name="hapu_id"/>
-    <tableColumn id="3" name="iwi_id"/>
-    <tableColumn id="4" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Region" displayName="Region" ref="A1:D14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D14"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="region_id"/>
-    <tableColumn id="2" name="region_name"/>
-    <tableColumn id="3" name="tkm_url"/>
-    <tableColumn id="4" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Representative_Org" displayName="Representative_Org" ref="A1:U2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Representative_Org" displayName="Representative_Org" ref="A1:U2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:U2"/>
   <tableColumns count="21">
     <tableColumn id="1" name="org_id"/>
@@ -2699,6 +2864,175 @@
     <tableColumn id="19" name="website"/>
     <tableColumn id="20" name="tkm_last_updated"/>
     <tableColumn id="21" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Source" displayName="Source" ref="A1:H6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H6"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="source_id"/>
+    <tableColumn id="2" name="name"/>
+    <tableColumn id="3" name="type"/>
+    <tableColumn id="4" name="url"/>
+    <tableColumn id="5" name="licence"/>
+    <tableColumn id="6" name="colour"/>
+    <tableColumn id="7" name="retrieved"/>
+    <tableColumn id="8" name="weight_note"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Tupuna" displayName="Tupuna" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J2"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="tupuna_id"/>
+    <tableColumn id="2" name="name"/>
+    <tableColumn id="3" name="other_names"/>
+    <tableColumn id="4" name="born"/>
+    <tableColumn id="5" name="died"/>
+    <tableColumn id="6" name="birthplace"/>
+    <tableColumn id="7" name="mother"/>
+    <tableColumn id="8" name="father"/>
+    <tableColumn id="9" name="notes"/>
+    <tableColumn id="10" name="source"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Tupuna_Location" displayName="Tupuna_Location" ref="A1:J4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J4"/>
+  <tableColumns count="10">
+    <tableColumn id="1" name="link_id"/>
+    <tableColumn id="2" name="tupuna_id"/>
+    <tableColumn id="3" name="location_type"/>
+    <tableColumn id="4" name="location_ref"/>
+    <tableColumn id="5" name="location_detail"/>
+    <tableColumn id="6" name="latitude"/>
+    <tableColumn id="7" name="longitude"/>
+    <tableColumn id="8" name="relationship"/>
+    <tableColumn id="9" name="notes"/>
+    <tableColumn id="10" name="source"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Contact" displayName="Contact" ref="A1:G4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:G4"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="contact_id"/>
+    <tableColumn id="2" name="org_id"/>
+    <tableColumn id="3" name="role"/>
+    <tableColumn id="4" name="full_name"/>
+    <tableColumn id="5" name="phone"/>
+    <tableColumn id="6" name="email"/>
+    <tableColumn id="7" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Hapu" displayName="Hapu" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D11"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="hapu_id"/>
+    <tableColumn id="2" name="hapu_name"/>
+    <tableColumn id="3" name="iwi_id"/>
+    <tableColumn id="4" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Iwi" displayName="Iwi" ref="A1:M118" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:M118"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="iwi_id"/>
+    <tableColumn id="2" name="iwi_name"/>
+    <tableColumn id="3" name="primary_region_id"/>
+    <tableColumn id="4" name="tkm_url"/>
+    <tableColumn id="5" name="mfa_status"/>
+    <tableColumn id="6" name="population"/>
+    <tableColumn id="7" name="population_source"/>
+    <tableColumn id="8" name="rohe_description"/>
+    <tableColumn id="9" name="rohe_map_image_url"/>
+    <tableColumn id="10" name="rohe_document_url"/>
+    <tableColumn id="11" name="rohe_copyright_holder"/>
+    <tableColumn id="12" name="tkm_last_updated"/>
+    <tableColumn id="13" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Iwi_LocalAuthority" displayName="Iwi_LocalAuthority" ref="A1:C5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C5"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="iwi_id"/>
+    <tableColumn id="2" name="authority_type"/>
+    <tableColumn id="3" name="authority_name"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Iwi_Region" displayName="Iwi_Region" ref="A1:B128" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:B128"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="iwi_id"/>
+    <tableColumn id="2" name="region_id"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Marae" displayName="Marae" ref="A1:P15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:P15"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="marae_id"/>
+    <tableColumn id="2" name="marae_name"/>
+    <tableColumn id="3" name="wharenui"/>
+    <tableColumn id="4" name="marae_type"/>
+    <tableColumn id="5" name="address_line"/>
+    <tableColumn id="6" name="locality"/>
+    <tableColumn id="7" name="postcode"/>
+    <tableColumn id="8" name="region_council_area"/>
+    <tableColumn id="9" name="latitude"/>
+    <tableColumn id="10" name="longitude"/>
+    <tableColumn id="11" name="nztm_easting"/>
+    <tableColumn id="12" name="nztm_northing"/>
+    <tableColumn id="13" name="geocode_source"/>
+    <tableColumn id="14" name="geocode_accuracy"/>
+    <tableColumn id="15" name="tkm_url"/>
+    <tableColumn id="16" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Marae_Hapu" displayName="Marae_Hapu" ref="A1:D18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D18"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="marae_id"/>
+    <tableColumn id="2" name="hapu_id"/>
+    <tableColumn id="3" name="iwi_id"/>
+    <tableColumn id="4" name="notes"/>
+  </tableColumns>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Region" displayName="Region" ref="A1:D14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D14"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="region_id"/>
+    <tableColumn id="2" name="region_name"/>
+    <tableColumn id="3" name="tkm_url"/>
+    <tableColumn id="4" name="notes"/>
   </tableColumns>
 </table>
 </file>
@@ -2883,7 +3217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
@@ -3082,17 +3416,30 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3125,39 +3472,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
@@ -3165,16 +3512,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
@@ -3182,19 +3529,19 @@
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -3239,55 +3586,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4290,72 +4637,72 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -4381,110 +4728,110 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="28"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
       <c r="H2" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
       <c r="G3" s="8"/>
       <c r="H3" s="8" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8" t="n">
@@ -4494,12 +4841,604 @@
         <v>174.35</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="J4" s="8"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+  <tableParts>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>687</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+  <tableParts>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>727</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4532,171 +5471,171 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -4739,57 +5678,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -4803,16 +5742,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -4826,16 +5765,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -4849,16 +5788,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -4872,16 +5811,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -4895,16 +5834,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -4918,16 +5857,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -4941,16 +5880,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -4964,16 +5903,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -4987,55 +5926,55 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>5667</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -5049,16 +5988,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -5072,16 +6011,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -5095,16 +6034,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -5118,16 +6057,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -5141,16 +6080,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -5164,16 +6103,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -5187,16 +6126,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -5210,16 +6149,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -5233,16 +6172,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -5256,16 +6195,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -5279,16 +6218,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -5302,16 +6241,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -5325,16 +6264,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -5348,16 +6287,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -5371,16 +6310,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -5394,16 +6333,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -5417,16 +6356,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -5440,16 +6379,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -5463,16 +6402,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -5486,16 +6425,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -5509,16 +6448,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -5532,16 +6471,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -5555,16 +6494,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -5578,16 +6517,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -5601,16 +6540,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -5624,16 +6563,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -5647,16 +6586,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -5670,16 +6609,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -5693,16 +6632,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -5716,16 +6655,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -5739,16 +6678,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -5762,16 +6701,16 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -5785,16 +6724,16 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -5808,16 +6747,16 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -5831,16 +6770,16 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -5854,16 +6793,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -5877,16 +6816,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -5900,16 +6839,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -5923,16 +6862,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -5946,16 +6885,16 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
@@ -5969,16 +6908,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
@@ -5992,16 +6931,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -6015,16 +6954,16 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -6038,16 +6977,16 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -6061,16 +7000,16 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -6084,16 +7023,16 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
@@ -6107,16 +7046,16 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -6130,16 +7069,16 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -6153,16 +7092,16 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -6176,16 +7115,16 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -6199,16 +7138,16 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
@@ -6222,16 +7161,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
@@ -6245,16 +7184,16 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -6268,16 +7207,16 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -6291,16 +7230,16 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -6314,16 +7253,16 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -6337,16 +7276,16 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
@@ -6360,16 +7299,16 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
@@ -6383,16 +7322,16 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
@@ -6406,16 +7345,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
@@ -6429,16 +7368,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -6452,16 +7391,16 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -6475,16 +7414,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -6498,16 +7437,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
@@ -6521,16 +7460,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
@@ -6544,16 +7483,16 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
@@ -6567,16 +7506,16 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
@@ -6590,16 +7529,16 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
@@ -6613,16 +7552,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
@@ -6636,16 +7575,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
@@ -6659,16 +7598,16 @@
     </row>
     <row r="83" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
@@ -6682,16 +7621,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
@@ -6705,16 +7644,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
@@ -6728,16 +7667,16 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
@@ -6751,16 +7690,16 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
@@ -6774,16 +7713,16 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
@@ -6797,16 +7736,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
@@ -6820,16 +7759,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
@@ -6843,16 +7782,16 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
@@ -6866,16 +7805,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
@@ -6889,16 +7828,16 @@
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -6912,16 +7851,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
@@ -6935,16 +7874,16 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
@@ -6958,16 +7897,16 @@
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
@@ -6981,16 +7920,16 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
@@ -7004,16 +7943,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
@@ -7027,16 +7966,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
@@ -7050,16 +7989,16 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
@@ -7073,16 +8012,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -7096,16 +8035,16 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
@@ -7119,16 +8058,16 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
@@ -7142,16 +8081,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
@@ -7165,16 +8104,16 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
@@ -7188,16 +8127,16 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
@@ -7211,16 +8150,16 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
@@ -7234,16 +8173,16 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
@@ -7257,16 +8196,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
@@ -7280,16 +8219,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
@@ -7303,16 +8242,16 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -7326,16 +8265,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -7349,16 +8288,16 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
@@ -7372,16 +8311,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
@@ -7395,16 +8334,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
@@ -7418,16 +8357,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
@@ -7441,16 +8380,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
@@ -7464,16 +8403,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
@@ -7514,1026 +8453,1026 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -8566,57 +9505,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -8650,135 +9589,135 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D11" s="8"/>
     </row>
@@ -8822,74 +9761,74 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
@@ -8898,32 +9837,32 @@
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
       <c r="O2" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>504</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I3" s="9"/>
       <c r="J3" s="9"/>
@@ -8932,32 +9871,32 @@
       <c r="M3" s="9"/>
       <c r="N3" s="9"/>
       <c r="O3" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
@@ -8966,32 +9905,32 @@
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
       <c r="O4" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>519</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>516</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I5" s="9"/>
       <c r="J5" s="9"/>
@@ -9000,32 +9939,32 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
       <c r="O5" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
@@ -9034,32 +9973,32 @@
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
       <c r="O6" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -9068,32 +10007,32 @@
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -9102,32 +10041,32 @@
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
@@ -9136,32 +10075,32 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -9170,32 +10109,32 @@
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
       <c r="O10" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -9204,32 +10143,32 @@
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
       <c r="O11" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -9238,32 +10177,32 @@
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
       <c r="O12" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -9272,30 +10211,30 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
@@ -9304,32 +10243,32 @@
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
       <c r="O14" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -9338,7 +10277,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="P15" s="8"/>
     </row>
@@ -9371,219 +10310,219 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D18" s="8"/>
     </row>
@@ -9626,127 +10565,127 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N2" s="8"/>
       <c r="O2" s="8" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="R2" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="T2" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U2" s="8"/>
     </row>

--- a/TKM_Iwi_Hapu_Marae_Database.xlsx
+++ b/TKM_Iwi_Hapu_Marae_Database.xlsx
@@ -377,7 +377,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13823" uniqueCount="3412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14267" uniqueCount="3492">
   <si>
     <t xml:space="preserve">TKM Iwi / Hapū / Marae Database</t>
   </si>
@@ -10484,6 +10484,246 @@
   </si>
   <si>
     <t xml:space="preserve">Ngāti Te Maunga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araiteuru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/araiteuru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moeraki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arahura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uruao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/uruao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ōtākou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Ruahikihiki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Tauraka Waka a Māui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kāti Māhaki ki Makaawhio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wairewa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngāti Irakēhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waitaha, Ngati Mamoe, Ngāi Tahu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Māori Maps writes 'Ngāti Irakēhu (Waitaha, Ngati Mamoe, Ngāi Tahu)'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nukutaimemeha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/nukutaimemeha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uepōhatu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereānini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/tereānini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matawhaorua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/matawhaorua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tauira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/tauira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tauira-mai-tawhiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/tauira-mai-tawhiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nukutere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/nukutere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/tauria-mai-tawhiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Māori Maps variant page "Tauria-mai-tawhiti" (typo for Tauira-mai-tawhiti)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Te Awatea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maorimaps.com/en/waka/te-awatea</t>
   </si>
   <si>
     <t xml:space="preserve">alias_id</t>
@@ -10887,8 +11127,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Claim" displayName="Claim" ref="A1:L1339" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:L1339"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Claim" displayName="Claim" ref="A1:L1388" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:L1388"/>
   <tableColumns count="12">
     <tableColumn id="1" name="claim_id"/>
     <tableColumn id="2" name="source_id"/>
@@ -13130,7 +13370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1339"/>
+  <dimension ref="A1:L1388"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="9"/>
@@ -56876,6 +57116,1580 @@
         <v>703</v>
       </c>
       <c r="L1339" s="4"/>
+    </row>
+    <row r="1340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1340" s="4" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B1340" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1340" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1340" s="4" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E1340" s="4"/>
+      <c r="F1340" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1340" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1340" s="4"/>
+      <c r="I1340" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1340" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1340" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1340" s="4"/>
+    </row>
+    <row r="1341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1341" s="4" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B1341" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1341" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1341" s="4" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E1341" s="4"/>
+      <c r="F1341" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1341" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1341" s="4"/>
+      <c r="I1341" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1341" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1341" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1341" s="4"/>
+    </row>
+    <row r="1342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1342" s="4" t="s">
+        <v>3373</v>
+      </c>
+      <c r="B1342" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1342" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1342" s="4" t="s">
+        <v>3374</v>
+      </c>
+      <c r="E1342" s="4"/>
+      <c r="F1342" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1342" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1342" s="4"/>
+      <c r="I1342" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1342" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1342" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1342" s="4"/>
+    </row>
+    <row r="1343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1343" s="4" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B1343" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1343" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1343" s="4" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1343" s="4"/>
+      <c r="F1343" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1343" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1343" s="4"/>
+      <c r="I1343" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1343" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1343" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1343" s="4"/>
+    </row>
+    <row r="1344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1344" s="4" t="s">
+        <v>3376</v>
+      </c>
+      <c r="B1344" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1344" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1344" s="4" t="s">
+        <v>2324</v>
+      </c>
+      <c r="E1344" s="4"/>
+      <c r="F1344" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1344" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1344" s="4"/>
+      <c r="I1344" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1344" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1344" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1344" s="4"/>
+    </row>
+    <row r="1345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1345" s="4" t="s">
+        <v>3377</v>
+      </c>
+      <c r="B1345" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1345" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1345" s="4" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E1345" s="4"/>
+      <c r="F1345" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1345" s="4" t="s">
+        <v>3370</v>
+      </c>
+      <c r="H1345" s="4"/>
+      <c r="I1345" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="J1345" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1345" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1345" s="4"/>
+    </row>
+    <row r="1346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1346" s="4" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B1346" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1346" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1346" s="4" t="s">
+        <v>3379</v>
+      </c>
+      <c r="E1346" s="4"/>
+      <c r="F1346" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1346" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1346" s="4"/>
+      <c r="I1346" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1346" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1346" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1346" s="4"/>
+    </row>
+    <row r="1347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1347" s="4" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B1347" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1347" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1347" s="4" t="s">
+        <v>3379</v>
+      </c>
+      <c r="E1347" s="4"/>
+      <c r="F1347" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1347" s="4" t="s">
+        <v>3286</v>
+      </c>
+      <c r="H1347" s="4"/>
+      <c r="I1347" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1347" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1347" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1347" s="4"/>
+    </row>
+    <row r="1348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1348" s="4" t="s">
+        <v>3383</v>
+      </c>
+      <c r="B1348" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1348" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1348" s="4" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E1348" s="4"/>
+      <c r="F1348" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1348" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1348" s="4"/>
+      <c r="I1348" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1348" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1348" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1348" s="4"/>
+    </row>
+    <row r="1349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1349" s="4" t="s">
+        <v>3384</v>
+      </c>
+      <c r="B1349" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1349" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1349" s="4" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1349" s="4"/>
+      <c r="F1349" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1349" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1349" s="4"/>
+      <c r="I1349" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1349" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1349" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1349" s="4"/>
+    </row>
+    <row r="1350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1350" s="4" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B1350" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1350" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1350" s="4" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E1350" s="4"/>
+      <c r="F1350" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1350" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1350" s="4"/>
+      <c r="I1350" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1350" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1350" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1350" s="4"/>
+    </row>
+    <row r="1351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1351" s="4" t="s">
+        <v>3386</v>
+      </c>
+      <c r="B1351" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1351" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1351" s="4" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E1351" s="4"/>
+      <c r="F1351" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1351" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1351" s="4"/>
+      <c r="I1351" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1351" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1351" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1351" s="4"/>
+    </row>
+    <row r="1352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1352" s="4" t="s">
+        <v>3388</v>
+      </c>
+      <c r="B1352" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1352" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1352" s="4" t="s">
+        <v>3387</v>
+      </c>
+      <c r="E1352" s="4"/>
+      <c r="F1352" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1352" s="4" t="s">
+        <v>3389</v>
+      </c>
+      <c r="H1352" s="4"/>
+      <c r="I1352" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1352" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1352" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1352" s="4"/>
+    </row>
+    <row r="1353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1353" s="4" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B1353" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1353" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1353" s="4" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E1353" s="4"/>
+      <c r="F1353" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1353" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1353" s="4"/>
+      <c r="I1353" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1353" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1353" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1353" s="4"/>
+    </row>
+    <row r="1354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1354" s="4" t="s">
+        <v>3391</v>
+      </c>
+      <c r="B1354" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1354" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1354" s="4" t="s">
+        <v>2402</v>
+      </c>
+      <c r="E1354" s="4"/>
+      <c r="F1354" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1354" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1354" s="4"/>
+      <c r="I1354" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1354" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1354" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1354" s="4"/>
+    </row>
+    <row r="1355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1355" s="4" t="s">
+        <v>3392</v>
+      </c>
+      <c r="B1355" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1355" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1355" s="4" t="s">
+        <v>3393</v>
+      </c>
+      <c r="E1355" s="4"/>
+      <c r="F1355" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1355" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1355" s="4"/>
+      <c r="I1355" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1355" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1355" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1355" s="4"/>
+    </row>
+    <row r="1356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1356" s="4" t="s">
+        <v>3394</v>
+      </c>
+      <c r="B1356" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1356" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1356" s="4" t="s">
+        <v>3393</v>
+      </c>
+      <c r="E1356" s="4"/>
+      <c r="F1356" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1356" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="H1356" s="4"/>
+      <c r="I1356" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1356" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1356" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1356" s="4"/>
+    </row>
+    <row r="1357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1357" s="4" t="s">
+        <v>3396</v>
+      </c>
+      <c r="B1357" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1357" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1357" s="4" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E1357" s="4"/>
+      <c r="F1357" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1357" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1357" s="4"/>
+      <c r="I1357" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1357" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1357" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1357" s="4"/>
+    </row>
+    <row r="1358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1358" s="4" t="s">
+        <v>3397</v>
+      </c>
+      <c r="B1358" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1358" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1358" s="4" t="s">
+        <v>3398</v>
+      </c>
+      <c r="E1358" s="4"/>
+      <c r="F1358" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1358" s="4" t="s">
+        <v>3380</v>
+      </c>
+      <c r="H1358" s="4"/>
+      <c r="I1358" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1358" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1358" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1358" s="4"/>
+    </row>
+    <row r="1359" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1359" s="4" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B1359" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1359" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1359" s="4" t="s">
+        <v>3398</v>
+      </c>
+      <c r="E1359" s="4"/>
+      <c r="F1359" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1359" s="4" t="s">
+        <v>3400</v>
+      </c>
+      <c r="H1359" s="4" t="s">
+        <v>3401</v>
+      </c>
+      <c r="I1359" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="J1359" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1359" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1359" s="4" t="s">
+        <v>3402</v>
+      </c>
+    </row>
+    <row r="1360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1360" s="4" t="s">
+        <v>3403</v>
+      </c>
+      <c r="B1360" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1360" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1360" s="4" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E1360" s="4"/>
+      <c r="F1360" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1360" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H1360" s="4"/>
+      <c r="I1360" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1360" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1360" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1360" s="4"/>
+    </row>
+    <row r="1361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1361" s="4" t="s">
+        <v>3406</v>
+      </c>
+      <c r="B1361" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1361" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1361" s="4" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E1361" s="4"/>
+      <c r="F1361" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1361" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H1361" s="4"/>
+      <c r="I1361" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1361" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1361" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1361" s="4"/>
+    </row>
+    <row r="1362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1362" s="4" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B1362" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1362" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1362" s="4" t="s">
+        <v>2388</v>
+      </c>
+      <c r="E1362" s="4"/>
+      <c r="F1362" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1362" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H1362" s="4"/>
+      <c r="I1362" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1362" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1362" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1362" s="4"/>
+    </row>
+    <row r="1363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1363" s="4" t="s">
+        <v>3408</v>
+      </c>
+      <c r="B1363" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1363" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1363" s="4" t="s">
+        <v>3409</v>
+      </c>
+      <c r="E1363" s="4"/>
+      <c r="F1363" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1363" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H1363" s="4"/>
+      <c r="I1363" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1363" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1363" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1363" s="4"/>
+    </row>
+    <row r="1364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1364" s="4" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B1364" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1364" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1364" s="4" t="s">
+        <v>3409</v>
+      </c>
+      <c r="E1364" s="4"/>
+      <c r="F1364" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="G1364" s="4" t="s">
+        <v>2950</v>
+      </c>
+      <c r="H1364" s="4"/>
+      <c r="I1364" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1364" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1364" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1364" s="4"/>
+    </row>
+    <row r="1365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1365" s="4" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B1365" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1365" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1365" s="4" t="s">
+        <v>2948</v>
+      </c>
+      <c r="E1365" s="4"/>
+      <c r="F1365" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1365" s="4" t="s">
+        <v>3404</v>
+      </c>
+      <c r="H1365" s="4"/>
+      <c r="I1365" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="J1365" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1365" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1365" s="4"/>
+    </row>
+    <row r="1366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1366" s="4" t="s">
+        <v>3412</v>
+      </c>
+      <c r="B1366" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1366" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1366" s="4" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E1366" s="4"/>
+      <c r="F1366" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1366" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="H1366" s="4"/>
+      <c r="I1366" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="J1366" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1366" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1366" s="4"/>
+    </row>
+    <row r="1367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1367" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="B1367" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1367" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1367" s="4" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E1367" s="4"/>
+      <c r="F1367" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1367" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="H1367" s="4"/>
+      <c r="I1367" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="J1367" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1367" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1367" s="4"/>
+    </row>
+    <row r="1368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1368" s="4" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B1368" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1368" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1368" s="4" t="s">
+        <v>2388</v>
+      </c>
+      <c r="E1368" s="4"/>
+      <c r="F1368" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1368" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="H1368" s="4"/>
+      <c r="I1368" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="J1368" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1368" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1368" s="4"/>
+    </row>
+    <row r="1369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1369" s="4" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B1369" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1369" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1369" s="4" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E1369" s="4"/>
+      <c r="F1369" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1369" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="H1369" s="4"/>
+      <c r="I1369" s="4" t="s">
+        <v>3414</v>
+      </c>
+      <c r="J1369" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1369" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1369" s="4"/>
+    </row>
+    <row r="1370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1370" s="4" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B1370" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1370" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1370" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E1370" s="4"/>
+      <c r="F1370" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1370" s="4" t="s">
+        <v>3419</v>
+      </c>
+      <c r="H1370" s="4"/>
+      <c r="I1370" s="4" t="s">
+        <v>3420</v>
+      </c>
+      <c r="J1370" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1370" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1370" s="4"/>
+    </row>
+    <row r="1371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1371" s="4" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B1371" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1371" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1371" s="4" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E1371" s="4"/>
+      <c r="F1371" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1371" s="4" t="s">
+        <v>3422</v>
+      </c>
+      <c r="H1371" s="4"/>
+      <c r="I1371" s="4" t="s">
+        <v>3423</v>
+      </c>
+      <c r="J1371" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1371" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1371" s="4"/>
+    </row>
+    <row r="1372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1372" s="4" t="s">
+        <v>3424</v>
+      </c>
+      <c r="B1372" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1372" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1372" s="4" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E1372" s="4"/>
+      <c r="F1372" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1372" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1372" s="4"/>
+      <c r="I1372" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1372" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1372" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1372" s="4"/>
+    </row>
+    <row r="1373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1373" s="4" t="s">
+        <v>3427</v>
+      </c>
+      <c r="B1373" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1373" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1373" s="4" t="s">
+        <v>1727</v>
+      </c>
+      <c r="E1373" s="4"/>
+      <c r="F1373" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1373" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1373" s="4"/>
+      <c r="I1373" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1373" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1373" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1373" s="4"/>
+    </row>
+    <row r="1374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1374" s="4" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B1374" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1374" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1374" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="E1374" s="4"/>
+      <c r="F1374" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1374" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1374" s="4"/>
+      <c r="I1374" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1374" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1374" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1374" s="4"/>
+    </row>
+    <row r="1375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1375" s="4" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B1375" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1375" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1375" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E1375" s="4"/>
+      <c r="F1375" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1375" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1375" s="4"/>
+      <c r="I1375" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1375" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1375" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1375" s="4"/>
+    </row>
+    <row r="1376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1376" s="4" t="s">
+        <v>3430</v>
+      </c>
+      <c r="B1376" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1376" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1376" s="4" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E1376" s="4"/>
+      <c r="F1376" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1376" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1376" s="4"/>
+      <c r="I1376" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1376" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1376" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1376" s="4"/>
+    </row>
+    <row r="1377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1377" s="4" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B1377" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1377" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1377" s="4" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E1377" s="4"/>
+      <c r="F1377" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1377" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1377" s="4"/>
+      <c r="I1377" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1377" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1377" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1377" s="4"/>
+    </row>
+    <row r="1378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1378" s="4" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B1378" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1378" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1378" s="4" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E1378" s="4"/>
+      <c r="F1378" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1378" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1378" s="4"/>
+      <c r="I1378" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1378" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1378" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1378" s="4"/>
+    </row>
+    <row r="1379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1379" s="4" t="s">
+        <v>3433</v>
+      </c>
+      <c r="B1379" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1379" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1379" s="4" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E1379" s="4"/>
+      <c r="F1379" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1379" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1379" s="4"/>
+      <c r="I1379" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1379" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1379" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1379" s="4"/>
+    </row>
+    <row r="1380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1380" s="4" t="s">
+        <v>3434</v>
+      </c>
+      <c r="B1380" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1380" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1380" s="4" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E1380" s="4"/>
+      <c r="F1380" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1380" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1380" s="4"/>
+      <c r="I1380" s="4" t="s">
+        <v>3426</v>
+      </c>
+      <c r="J1380" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1380" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1380" s="4"/>
+    </row>
+    <row r="1381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1381" s="4" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B1381" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1381" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1381" s="4" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1381" s="4"/>
+      <c r="F1381" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1381" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1381" s="4"/>
+      <c r="I1381" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1381" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1381" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1381" s="4"/>
+    </row>
+    <row r="1382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1382" s="4" t="s">
+        <v>3438</v>
+      </c>
+      <c r="B1382" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1382" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1382" s="4" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E1382" s="4"/>
+      <c r="F1382" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1382" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1382" s="4"/>
+      <c r="I1382" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1382" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1382" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1382" s="4"/>
+    </row>
+    <row r="1383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1383" s="4" t="s">
+        <v>3439</v>
+      </c>
+      <c r="B1383" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1383" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1383" s="4" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E1383" s="4"/>
+      <c r="F1383" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1383" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1383" s="4"/>
+      <c r="I1383" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1383" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1383" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1383" s="4"/>
+    </row>
+    <row r="1384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1384" s="4" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B1384" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1384" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1384" s="4" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E1384" s="4"/>
+      <c r="F1384" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1384" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1384" s="4"/>
+      <c r="I1384" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1384" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1384" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1384" s="4"/>
+    </row>
+    <row r="1385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1385" s="4" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B1385" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1385" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1385" s="4" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E1385" s="4"/>
+      <c r="F1385" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1385" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1385" s="4"/>
+      <c r="I1385" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1385" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1385" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1385" s="4"/>
+    </row>
+    <row r="1386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1386" s="4" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B1386" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1386" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1386" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E1386" s="4"/>
+      <c r="F1386" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1386" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="H1386" s="4"/>
+      <c r="I1386" s="4" t="s">
+        <v>3437</v>
+      </c>
+      <c r="J1386" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1386" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1386" s="4"/>
+    </row>
+    <row r="1387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1387" s="4" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B1387" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1387" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1387" s="4" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E1387" s="4"/>
+      <c r="F1387" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1387" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="H1387" s="4"/>
+      <c r="I1387" s="4" t="s">
+        <v>3444</v>
+      </c>
+      <c r="J1387" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1387" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1387" s="4" t="s">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1388" s="4" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B1388" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="C1388" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1388" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E1388" s="4"/>
+      <c r="F1388" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="G1388" s="4" t="s">
+        <v>3447</v>
+      </c>
+      <c r="H1388" s="4"/>
+      <c r="I1388" s="4" t="s">
+        <v>3448</v>
+      </c>
+      <c r="J1388" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K1388" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="L1388" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -56900,25 +58714,25 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>3369</v>
+        <v>3449</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>3370</v>
+        <v>3450</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>3371</v>
+        <v>3451</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>3372</v>
+        <v>3452</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>696</v>
@@ -56927,9 +58741,9 @@
         <v>647</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>3373</v>
+        <v>3453</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>905</v>
@@ -56938,18 +58752,18 @@
         <v>860</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>3375</v>
+        <v>3455</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>3376</v>
+        <v>3456</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1008</v>
@@ -56958,18 +58772,18 @@
         <v>1056</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>3377</v>
+        <v>3457</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>3378</v>
+        <v>3458</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1138</v>
@@ -56978,18 +58792,18 @@
         <v>1151</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>3379</v>
+        <v>3459</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>3380</v>
+        <v>3460</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>1207</v>
@@ -56998,112 +58812,112 @@
         <v>990</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>3381</v>
+        <v>3461</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>3382</v>
+        <v>3462</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>1143</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>3383</v>
+        <v>3463</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>3384</v>
+        <v>3464</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>3385</v>
+        <v>3465</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>913</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>3386</v>
+        <v>3466</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>3387</v>
+        <v>3467</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3385</v>
+        <v>3465</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>3388</v>
+        <v>3468</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>3389</v>
+        <v>3469</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>3390</v>
+        <v>3470</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>1196</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>3391</v>
+        <v>3471</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>3392</v>
+        <v>3472</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>3393</v>
+        <v>3473</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>3394</v>
+        <v>3474</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>848</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>3395</v>
+        <v>3475</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>3396</v>
+        <v>3476</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>930</v>
@@ -57112,18 +58926,18 @@
         <v>1263</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>3397</v>
+        <v>3477</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>3398</v>
+        <v>3478</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>1114</v>
@@ -57132,18 +58946,18 @@
         <v>786</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>3399</v>
+        <v>3479</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>3400</v>
+        <v>3480</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>1228</v>
@@ -57152,16 +58966,16 @@
         <v>768</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>3401</v>
+        <v>3481</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>2437</v>
@@ -57170,36 +58984,36 @@
         <v>2434</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>3374</v>
+        <v>3454</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>3402</v>
+        <v>3482</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>3403</v>
+        <v>3483</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>3404</v>
+        <v>3484</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>2828</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>3405</v>
+        <v>3485</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>3406</v>
+        <v>3486</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>1504</v>
@@ -57208,18 +59022,18 @@
         <v>2345</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>3407</v>
+        <v>3487</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>3408</v>
+        <v>3488</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>3409</v>
+        <v>3489</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>108</v>
@@ -57228,10 +59042,10 @@
         <v>2018</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>3410</v>
+        <v>3490</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>3411</v>
+        <v>3491</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>669</v>

--- a/TKM_Iwi_Hapu_Marae_Database.xlsx
+++ b/TKM_Iwi_Hapu_Marae_Database.xlsx
@@ -114,7 +114,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Links a tupuna to any number of locations of interest. location_type: Marae | Hapū | Iwi | Place. location_ref: the marae/hapū/iwi name exactly as on the map, or a label for a Place. location_detail: for marae, the Location text as shown on the map (disambiguates same-name marae). latitude/longitude: only for Place. relationship: Born | Lived | Died | Buried | Affiliated | Land interest | Other.</t>
+          <t xml:space="preserve">Links a tupuna to any number of locations of interest OR to another tupuna. location_type: Marae | Hapū | Iwi | Waka | Place | Tupuna. location_ref: the marae/hapū/iwi/waka name as on the map, a label for a Place, or the other tupuna's tupuna_id (location_detail = their name). latitude/longitude: Place only. relationship — for locations: Born | Lived | Died | Buried | Affiliated | Land interest | Other; for Tupuna: Mother | Father | Child | Spouse / partner | Sibling | Grandparent | Grandchild | Ancestor | Descendant | Whāngai | Other (recorded from this tupuna's point of view; the map shows the inverse on the other card).</t>
         </r>
       </text>
     </comment>
@@ -57117,7 +57117,7 @@
       </c>
       <c r="L1339" s="4"/>
     </row>
-    <row r="1340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1340" s="4" t="s">
         <v>3369</v>
       </c>
@@ -57149,7 +57149,7 @@
       </c>
       <c r="L1340" s="4"/>
     </row>
-    <row r="1341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1341" s="4" t="s">
         <v>3372</v>
       </c>
@@ -57181,7 +57181,7 @@
       </c>
       <c r="L1341" s="4"/>
     </row>
-    <row r="1342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1342" s="4" t="s">
         <v>3373</v>
       </c>
@@ -57213,7 +57213,7 @@
       </c>
       <c r="L1342" s="4"/>
     </row>
-    <row r="1343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1343" s="4" t="s">
         <v>3375</v>
       </c>
@@ -57245,7 +57245,7 @@
       </c>
       <c r="L1343" s="4"/>
     </row>
-    <row r="1344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1344" s="4" t="s">
         <v>3376</v>
       </c>
@@ -57277,7 +57277,7 @@
       </c>
       <c r="L1344" s="4"/>
     </row>
-    <row r="1345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1345" s="4" t="s">
         <v>3377</v>
       </c>
@@ -57309,7 +57309,7 @@
       </c>
       <c r="L1345" s="4"/>
     </row>
-    <row r="1346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1346" s="4" t="s">
         <v>3378</v>
       </c>
@@ -57341,7 +57341,7 @@
       </c>
       <c r="L1346" s="4"/>
     </row>
-    <row r="1347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1347" s="4" t="s">
         <v>3382</v>
       </c>
@@ -57373,7 +57373,7 @@
       </c>
       <c r="L1347" s="4"/>
     </row>
-    <row r="1348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1348" s="4" t="s">
         <v>3383</v>
       </c>
@@ -57405,7 +57405,7 @@
       </c>
       <c r="L1348" s="4"/>
     </row>
-    <row r="1349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1349" s="4" t="s">
         <v>3384</v>
       </c>
@@ -57437,7 +57437,7 @@
       </c>
       <c r="L1349" s="4"/>
     </row>
-    <row r="1350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1350" s="4" t="s">
         <v>3385</v>
       </c>
@@ -57469,7 +57469,7 @@
       </c>
       <c r="L1350" s="4"/>
     </row>
-    <row r="1351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1351" s="4" t="s">
         <v>3386</v>
       </c>
@@ -57501,7 +57501,7 @@
       </c>
       <c r="L1351" s="4"/>
     </row>
-    <row r="1352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1352" s="4" t="s">
         <v>3388</v>
       </c>
@@ -57533,7 +57533,7 @@
       </c>
       <c r="L1352" s="4"/>
     </row>
-    <row r="1353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1353" s="4" t="s">
         <v>3390</v>
       </c>
@@ -57565,7 +57565,7 @@
       </c>
       <c r="L1353" s="4"/>
     </row>
-    <row r="1354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1354" s="4" t="s">
         <v>3391</v>
       </c>
@@ -57597,7 +57597,7 @@
       </c>
       <c r="L1354" s="4"/>
     </row>
-    <row r="1355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1355" s="4" t="s">
         <v>3392</v>
       </c>
@@ -57629,7 +57629,7 @@
       </c>
       <c r="L1355" s="4"/>
     </row>
-    <row r="1356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1356" s="4" t="s">
         <v>3394</v>
       </c>
@@ -57661,7 +57661,7 @@
       </c>
       <c r="L1356" s="4"/>
     </row>
-    <row r="1357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1357" s="4" t="s">
         <v>3396</v>
       </c>
@@ -57693,7 +57693,7 @@
       </c>
       <c r="L1357" s="4"/>
     </row>
-    <row r="1358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1358" s="4" t="s">
         <v>3397</v>
       </c>
@@ -57725,7 +57725,7 @@
       </c>
       <c r="L1358" s="4"/>
     </row>
-    <row r="1359" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1359" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1359" s="4" t="s">
         <v>3399</v>
       </c>
@@ -57761,7 +57761,7 @@
         <v>3402</v>
       </c>
     </row>
-    <row r="1360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1360" s="4" t="s">
         <v>3403</v>
       </c>
@@ -57793,7 +57793,7 @@
       </c>
       <c r="L1360" s="4"/>
     </row>
-    <row r="1361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1361" s="4" t="s">
         <v>3406</v>
       </c>
@@ -57825,7 +57825,7 @@
       </c>
       <c r="L1361" s="4"/>
     </row>
-    <row r="1362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1362" s="4" t="s">
         <v>3407</v>
       </c>
@@ -57857,7 +57857,7 @@
       </c>
       <c r="L1362" s="4"/>
     </row>
-    <row r="1363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1363" s="4" t="s">
         <v>3408</v>
       </c>
@@ -57889,7 +57889,7 @@
       </c>
       <c r="L1363" s="4"/>
     </row>
-    <row r="1364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1364" s="4" t="s">
         <v>3410</v>
       </c>
@@ -57921,7 +57921,7 @@
       </c>
       <c r="L1364" s="4"/>
     </row>
-    <row r="1365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1365" s="4" t="s">
         <v>3411</v>
       </c>
@@ -57953,7 +57953,7 @@
       </c>
       <c r="L1365" s="4"/>
     </row>
-    <row r="1366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1366" s="4" t="s">
         <v>3412</v>
       </c>
@@ -57985,7 +57985,7 @@
       </c>
       <c r="L1366" s="4"/>
     </row>
-    <row r="1367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1367" s="4" t="s">
         <v>3415</v>
       </c>
@@ -58017,7 +58017,7 @@
       </c>
       <c r="L1367" s="4"/>
     </row>
-    <row r="1368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1368" s="4" t="s">
         <v>3416</v>
       </c>
@@ -58049,7 +58049,7 @@
       </c>
       <c r="L1368" s="4"/>
     </row>
-    <row r="1369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1369" s="4" t="s">
         <v>3417</v>
       </c>
@@ -58081,7 +58081,7 @@
       </c>
       <c r="L1369" s="4"/>
     </row>
-    <row r="1370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1370" s="4" t="s">
         <v>3418</v>
       </c>
@@ -58113,7 +58113,7 @@
       </c>
       <c r="L1370" s="4"/>
     </row>
-    <row r="1371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1371" s="4" t="s">
         <v>3421</v>
       </c>
@@ -58145,7 +58145,7 @@
       </c>
       <c r="L1371" s="4"/>
     </row>
-    <row r="1372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1372" s="4" t="s">
         <v>3424</v>
       </c>
@@ -58177,7 +58177,7 @@
       </c>
       <c r="L1372" s="4"/>
     </row>
-    <row r="1373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1373" s="4" t="s">
         <v>3427</v>
       </c>
@@ -58209,7 +58209,7 @@
       </c>
       <c r="L1373" s="4"/>
     </row>
-    <row r="1374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1374" s="4" t="s">
         <v>3428</v>
       </c>
@@ -58241,7 +58241,7 @@
       </c>
       <c r="L1374" s="4"/>
     </row>
-    <row r="1375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1375" s="4" t="s">
         <v>3429</v>
       </c>
@@ -58273,7 +58273,7 @@
       </c>
       <c r="L1375" s="4"/>
     </row>
-    <row r="1376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1376" s="4" t="s">
         <v>3430</v>
       </c>
@@ -58305,7 +58305,7 @@
       </c>
       <c r="L1376" s="4"/>
     </row>
-    <row r="1377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1377" s="4" t="s">
         <v>3431</v>
       </c>
@@ -58337,7 +58337,7 @@
       </c>
       <c r="L1377" s="4"/>
     </row>
-    <row r="1378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1378" s="4" t="s">
         <v>3432</v>
       </c>
@@ -58369,7 +58369,7 @@
       </c>
       <c r="L1378" s="4"/>
     </row>
-    <row r="1379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1379" s="4" t="s">
         <v>3433</v>
       </c>
@@ -58401,7 +58401,7 @@
       </c>
       <c r="L1379" s="4"/>
     </row>
-    <row r="1380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1380" s="4" t="s">
         <v>3434</v>
       </c>
@@ -58433,7 +58433,7 @@
       </c>
       <c r="L1380" s="4"/>
     </row>
-    <row r="1381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1381" s="4" t="s">
         <v>3435</v>
       </c>
@@ -58465,7 +58465,7 @@
       </c>
       <c r="L1381" s="4"/>
     </row>
-    <row r="1382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1382" s="4" t="s">
         <v>3438</v>
       </c>
@@ -58497,7 +58497,7 @@
       </c>
       <c r="L1382" s="4"/>
     </row>
-    <row r="1383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1383" s="4" t="s">
         <v>3439</v>
       </c>
@@ -58529,7 +58529,7 @@
       </c>
       <c r="L1383" s="4"/>
     </row>
-    <row r="1384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1384" s="4" t="s">
         <v>3440</v>
       </c>
@@ -58561,7 +58561,7 @@
       </c>
       <c r="L1384" s="4"/>
     </row>
-    <row r="1385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1385" s="4" t="s">
         <v>3441</v>
       </c>
@@ -58593,7 +58593,7 @@
       </c>
       <c r="L1385" s="4"/>
     </row>
-    <row r="1386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1386" s="4" t="s">
         <v>3442</v>
       </c>
@@ -58625,7 +58625,7 @@
       </c>
       <c r="L1386" s="4"/>
     </row>
-    <row r="1387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1387" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1387" s="4" t="s">
         <v>3443</v>
       </c>
@@ -58659,7 +58659,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="1388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1388" s="4" t="s">
         <v>3446</v>
       </c>
